--- a/data/trans_dic/P25A$rendimiento-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,16</t>
+          <t>0,0; 35,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,68</t>
+          <t>0,0; 34,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,15</t>
+          <t>0,0; 26,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,83</t>
+          <t>0,0; 35,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,08</t>
+          <t>0,0; 26,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,33</t>
+          <t>0,0; 23,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 25,34</t>
+          <t>2,39; 26,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,35</t>
+          <t>0,0; 24,06</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,56</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 13,36</t>
+          <t>2,41; 13,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 20,17</t>
+          <t>2,02; 19,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 17,37</t>
+          <t>3,12; 16,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,32</t>
+          <t>1,14; 7,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 14,51</t>
+          <t>4,34; 15,06</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,35</t>
+          <t>1,2; 10,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,79</t>
+          <t>0,81; 7,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 9,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,61</t>
+          <t>1,74; 13,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 10,53</t>
+          <t>1,6; 9,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,15</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 9,01</t>
+          <t>1,97; 8,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,36</t>
+          <t>1,63; 6,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,48</t>
+          <t>0,81; 6,72</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,15</t>
+          <t>1,25; 7,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,54</t>
+          <t>0,9; 8,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,9; 21,85</t>
+          <t>5,15; 22,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,89</t>
+          <t>1,16; 10,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 12,36</t>
+          <t>2,29; 13,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,62</t>
+          <t>1,6; 7,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,26</t>
+          <t>1,97; 6,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,49</t>
+          <t>2,12; 8,04</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,8</t>
+          <t>1,61; 9,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,72</t>
+          <t>0,75; 6,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,62</t>
+          <t>2,58; 12,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,33</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 11,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,08</t>
+          <t>0,0; 11,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,09</t>
+          <t>2,05; 8,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,26</t>
+          <t>0,96; 5,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,5</t>
+          <t>2,51; 9,9</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,25</t>
+          <t>2,14; 9,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,42; 10,33</t>
+          <t>2,4; 9,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,95</t>
+          <t>2,31; 11,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,68</t>
+          <t>0,0; 16,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,88</t>
+          <t>1,38; 8,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,66</t>
+          <t>2,32; 9,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,82</t>
+          <t>2,0; 9,88</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,48</t>
+          <t>0,81; 7,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,73</t>
+          <t>0,64; 6,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,23</t>
+          <t>1,74; 9,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,02</t>
+          <t>0,75; 6,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,16</t>
+          <t>0,61; 5,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 10,1</t>
+          <t>1,77; 9,04</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,88</t>
+          <t>2,06; 4,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,24</t>
+          <t>2,54; 5,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,42</t>
+          <t>3,39; 7,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,42</t>
+          <t>2,77; 8,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,66</t>
+          <t>1,69; 5,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,45</t>
+          <t>2,74; 7,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,01</t>
+          <t>2,65; 5,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,84</t>
+          <t>2,56; 4,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,54</t>
+          <t>3,51; 6,36</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la disminución del rendimiento (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4646</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5988</t>
+          <t>0; 5788</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1765,32 +1765,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4038</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7658</t>
+          <t>0; 6908</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 4316</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5970</t>
+          <t>0; 6407</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>897; 9125</t>
+          <t>860; 9478</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 6244</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4955</t>
+          <t>0; 4755</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1776; 9717</t>
+          <t>1756; 10006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1234; 9801</t>
+          <t>981; 9670</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1829; 10072</t>
+          <t>1810; 9533</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4950</t>
+          <t>0; 4304</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1024; 9828</t>
+          <t>1775; 10936</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4031; 15457</t>
+          <t>4621; 16054</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1006; 8791</t>
+          <t>1019; 8530</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>899; 7632</t>
+          <t>915; 8444</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7938</t>
+          <t>0; 6865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>959; 9017</t>
+          <t>1151; 9019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1927; 13071</t>
+          <t>1981; 12118</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7164</t>
+          <t>0; 7159</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3104; 13621</t>
+          <t>2986; 13332</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3722; 15031</t>
+          <t>3864; 15192</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1139; 10515</t>
+          <t>1321; 10908</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2267; 13852</t>
+          <t>2121; 12596</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>986; 9244</t>
+          <t>970; 8834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2877; 12838</t>
+          <t>3026; 13078</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1043; 9972</t>
+          <t>1062; 9597</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2006; 10907</t>
+          <t>2023; 11477</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3014; 14044</t>
+          <t>2953; 13932</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4998; 18988</t>
+          <t>5162; 17591</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4023; 16681</t>
+          <t>4158; 15784</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2091; 12559</t>
+          <t>2068; 12430</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1068; 9426</t>
+          <t>1050; 9507</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3298; 15458</t>
+          <t>3435; 16058</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>0; 4531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5690</t>
+          <t>0; 6034</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7446</t>
+          <t>0; 6639</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2815; 13232</t>
+          <t>2986; 12952</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1213; 12018</t>
+          <t>1852; 11297</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4875; 18044</t>
+          <t>4774; 18807</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2587; 11282</t>
+          <t>2614; 12005</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3941; 16786</t>
+          <t>3897; 15832</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2863; 13489</t>
+          <t>2848; 13647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1707</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1814</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4297</t>
+          <t>0; 4281</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2622; 12033</t>
+          <t>1867; 11213</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3837; 16735</t>
+          <t>4025; 16509</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3766; 14637</t>
+          <t>2973; 14719</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>874; 8476</t>
+          <t>921; 8959</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>919; 9523</t>
+          <t>911; 8664</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2396; 12211</t>
+          <t>1894; 10360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1693</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 1420</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>854; 8599</t>
+          <t>923; 7956</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>916; 7631</t>
+          <t>909; 8068</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2216; 11239</t>
+          <t>1966; 10055</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13128; 30466</t>
+          <t>12841; 29474</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19923; 42768</t>
+          <t>20728; 43390</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21916; 44924</t>
+          <t>20534; 43484</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7348; 21121</t>
+          <t>6940; 21806</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6864; 21879</t>
+          <t>6521; 20973</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9618; 25014</t>
+          <t>9209; 24915</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23317; 43831</t>
+          <t>23224; 43983</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>30754; 58175</t>
+          <t>30736; 57019</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35259; 61580</t>
+          <t>33082; 59840</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$rendimiento-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25A$rendimiento-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,58</t>
+          <t>0,0; 41,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,48</t>
+          <t>0,0; 33,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,97</t>
+          <t>0,0; 43,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,18</t>
+          <t>0,0; 29,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,92</t>
+          <t>0,0; 41,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,16</t>
+          <t>0,0; 25,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,97</t>
+          <t>0,0; 23,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 26,32</t>
+          <t>2,57; 29,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,06</t>
+          <t>0,0; 28,43</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 12,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 13,76</t>
+          <t>2,43; 13,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 19,9</t>
+          <t>2,06; 21,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 16,44</t>
+          <t>3,14; 17,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,03</t>
+          <t>1,16; 6,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 15,06</t>
+          <t>3,78; 14,57</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,04</t>
+          <t>1,19; 9,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,52</t>
+          <t>0,81; 6,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,24</t>
+          <t>0,0; 10,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 13,61</t>
+          <t>1,46; 14,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,77</t>
+          <t>1,77; 9,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 8,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,82</t>
+          <t>1,94; 9,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,43</t>
+          <t>1,64; 6,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,72</t>
+          <t>0,71; 6,21</t>
         </is>
       </c>
     </row>
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,41</t>
+          <t>1,26; 7,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,17</t>
+          <t>0,89; 7,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 22,26</t>
+          <t>4,76; 22,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,48</t>
+          <t>1,21; 11,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 13,01</t>
+          <t>2,26; 12,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,56</t>
+          <t>1,56; 7,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,73</t>
+          <t>1,64; 6,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,04</t>
+          <t>2,11; 7,89</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,7</t>
+          <t>1,61; 9,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,78</t>
+          <t>0,74; 6,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 12,07</t>
+          <t>2,18; 12,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,98</t>
+          <t>0,0; 20,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,66</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,66</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,9</t>
+          <t>1,98; 8,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,88</t>
+          <t>0,98; 5,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,9</t>
+          <t>2,29; 9,7</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,85</t>
+          <t>2,1; 9,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,74</t>
+          <t>1,89; 9,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 11,07</t>
+          <t>2,29; 10,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,62</t>
+          <t>0,0; 19,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,28</t>
+          <t>1,42; 8,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,53</t>
+          <t>2,28; 9,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,88</t>
+          <t>2,51; 9,38</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,91</t>
+          <t>0,76; 7,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,12</t>
+          <t>0,63; 5,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,53</t>
+          <t>2,17; 10,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,49</t>
+          <t>0,69; 6,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,46</t>
+          <t>0,61; 5,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,04</t>
+          <t>1,6; 9,47</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,72</t>
+          <t>2,09; 4,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,32</t>
+          <t>2,63; 5,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,39; 7,18</t>
+          <t>3,42; 7,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,7</t>
+          <t>2,81; 8,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,43</t>
+          <t>1,87; 5,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,42</t>
+          <t>2,92; 7,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,02</t>
+          <t>2,61; 5,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,74</t>
+          <t>2,64; 4,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,36</t>
+          <t>3,63; 6,53</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 4708</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5788</t>
+          <t>0; 5694</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4154</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>0; 4546</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6908</t>
+          <t>0; 8025</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4316</t>
+          <t>0; 4124</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6407</t>
+          <t>0; 6188</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>860; 9478</t>
+          <t>924; 10480</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6244</t>
+          <t>0; 7377</t>
         </is>
       </c>
     </row>
@@ -1913,17 +1913,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4755</t>
+          <t>0; 5049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1756; 10006</t>
+          <t>1768; 10130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>981; 9670</t>
+          <t>1000; 10471</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1810; 9533</t>
+          <t>1822; 10036</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4304</t>
+          <t>0; 4999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1775; 10936</t>
+          <t>1808; 10149</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4621; 16054</t>
+          <t>4033; 15531</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1019; 8530</t>
+          <t>1013; 8372</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>915; 8444</t>
+          <t>914; 7791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6865</t>
+          <t>0; 7501</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1151; 9019</t>
+          <t>967; 9666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1981; 12118</t>
+          <t>2194; 12111</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7159</t>
+          <t>0; 7213</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2986; 13332</t>
+          <t>2934; 14098</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3864; 15192</t>
+          <t>3873; 16031</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1321; 10908</t>
+          <t>1150; 10081</t>
         </is>
       </c>
     </row>
@@ -2244,42 +2244,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2121; 12596</t>
+          <t>2140; 12320</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>970; 8834</t>
+          <t>967; 8259</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3026; 13078</t>
+          <t>2797; 12946</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1062; 9597</t>
+          <t>1112; 10339</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2023; 11477</t>
+          <t>1996; 10604</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2953; 13932</t>
+          <t>2878; 13270</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5162; 17591</t>
+          <t>4301; 17443</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4158; 15784</t>
+          <t>4142; 15507</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2068; 12430</t>
+          <t>2057; 12373</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1050; 9507</t>
+          <t>1036; 9637</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3435; 16058</t>
+          <t>2897; 16441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 3613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6034</t>
+          <t>0; 5208</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6639</t>
+          <t>0; 6617</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2986; 12952</t>
+          <t>2886; 12907</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1852; 11297</t>
+          <t>1874; 11422</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4774; 18807</t>
+          <t>4343; 18430</t>
         </is>
       </c>
     </row>
@@ -2565,17 +2565,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2614; 12005</t>
+          <t>2554; 11913</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3897; 15832</t>
+          <t>3071; 15770</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2848; 13647</t>
+          <t>2826; 13186</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2590,22 +2590,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 5134</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1867; 11213</t>
+          <t>1918; 10859</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4025; 16509</t>
+          <t>3950; 15916</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2973; 14719</t>
+          <t>3738; 13976</t>
         </is>
       </c>
     </row>
@@ -2728,17 +2728,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>921; 8959</t>
+          <t>867; 8173</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>911; 8664</t>
+          <t>892; 8377</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1894; 10360</t>
+          <t>2363; 11553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>923; 7956</t>
+          <t>850; 8241</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>909; 8068</t>
+          <t>907; 8392</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1966; 10055</t>
+          <t>1777; 10532</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12841; 29474</t>
+          <t>13057; 30053</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20728; 43390</t>
+          <t>21455; 43465</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20534; 43484</t>
+          <t>20699; 42437</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6940; 21806</t>
+          <t>7051; 20533</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6521; 20973</t>
+          <t>7246; 23098</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9209; 24915</t>
+          <t>9792; 25595</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23224; 43983</t>
+          <t>22869; 44669</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>30736; 57019</t>
+          <t>31715; 59310</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33082; 59840</t>
+          <t>34159; 61460</t>
         </is>
       </c>
     </row>
